--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:02:23+00:00</t>
+    <t>2023-09-21T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T09:50:54+00:00</t>
+    <t>2023-09-21T10:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T10:44:28+00:00</t>
+    <t>2023-09-21T12:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T12:08:39+00:00</t>
+    <t>2023-09-21T12:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-21T14:50:45+00:00</t>
+    <t>2023-09-22T07:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T07:44:14+00:00</t>
+    <t>2023-09-22T09:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T09:20:33+00:00</t>
+    <t>2023-09-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="243">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T09:23:37+00:00</t>
+    <t>2023-09-22T12:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
+  </si>
+  <si>
+    <t>transaction</t>
   </si>
   <si>
     <t>required</t>
@@ -622,6 +625,9 @@
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+  </si>
+  <si>
+    <t>POST</t>
   </si>
   <si>
     <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
@@ -1843,7 +1849,7 @@
         <v>35</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="T7" t="s" s="2">
         <v>35</v>
@@ -1858,13 +1864,13 @@
         <v>35</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>35</v>
@@ -1906,15 +1912,15 @@
         <v>35</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1937,16 +1943,16 @@
         <v>46</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1996,7 +2002,7 @@
         <v>35</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
@@ -2017,18 +2023,18 @@
         <v>65</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2051,16 +2057,16 @@
         <v>46</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2110,7 +2116,7 @@
         <v>35</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -2119,7 +2125,7 @@
         <v>45</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>58</v>
@@ -2139,10 +2145,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2165,16 +2171,16 @@
         <v>46</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2224,7 +2230,7 @@
         <v>35</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -2253,10 +2259,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2279,13 +2285,13 @@
         <v>35</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2336,7 +2342,7 @@
         <v>35</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>36</v>
@@ -2365,14 +2371,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2391,16 +2397,16 @@
         <v>35</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2438,19 +2444,19 @@
         <v>35</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -2462,7 +2468,7 @@
         <v>57</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>35</v>
@@ -2479,14 +2485,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2505,19 +2511,19 @@
         <v>46</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>35</v>
@@ -2566,7 +2572,7 @@
         <v>35</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
@@ -2578,7 +2584,7 @@
         <v>57</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>35</v>
@@ -2595,10 +2601,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2621,16 +2627,16 @@
         <v>46</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2680,7 +2686,7 @@
         <v>35</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>45</v>
@@ -2709,10 +2715,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2738,13 +2744,13 @@
         <v>60</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2794,7 +2800,7 @@
         <v>35</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>45</v>
@@ -2823,10 +2829,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2849,13 +2855,13 @@
         <v>46</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2906,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
@@ -2918,7 +2924,7 @@
         <v>57</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>35</v>
@@ -2935,10 +2941,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2961,13 +2967,13 @@
         <v>35</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3018,7 +3024,7 @@
         <v>35</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
@@ -3047,14 +3053,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3073,16 +3079,16 @@
         <v>35</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3120,19 +3126,19 @@
         <v>35</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
@@ -3144,7 +3150,7 @@
         <v>57</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>35</v>
@@ -3161,14 +3167,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3187,19 +3193,19 @@
         <v>46</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>35</v>
@@ -3248,7 +3254,7 @@
         <v>35</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -3260,7 +3266,7 @@
         <v>57</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>35</v>
@@ -3277,10 +3283,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3306,10 +3312,10 @@
         <v>38</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3360,7 +3366,7 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
@@ -3389,10 +3395,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3418,13 +3424,13 @@
         <v>60</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3474,7 +3480,7 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -3503,10 +3509,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3514,7 +3520,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>45</v>
@@ -3529,16 +3535,16 @@
         <v>35</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3588,7 +3594,7 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -3600,16 +3606,16 @@
         <v>35</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>35</v>
@@ -3617,10 +3623,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3643,13 +3649,13 @@
         <v>46</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3700,7 +3706,7 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -3709,7 +3715,7 @@
         <v>45</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>58</v>
@@ -3729,10 +3735,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3755,13 +3761,13 @@
         <v>35</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3812,7 +3818,7 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -3841,14 +3847,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3867,16 +3873,16 @@
         <v>35</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3914,19 +3920,19 @@
         <v>35</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
@@ -3938,7 +3944,7 @@
         <v>57</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>35</v>
@@ -3955,14 +3961,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3981,19 +3987,19 @@
         <v>46</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>35</v>
@@ -4042,7 +4048,7 @@
         <v>35</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -4054,7 +4060,7 @@
         <v>57</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>35</v>
@@ -4071,10 +4077,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4100,13 +4106,13 @@
         <v>67</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4132,13 +4138,13 @@
         <v>35</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>35</v>
@@ -4156,7 +4162,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -4185,10 +4191,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4211,16 +4217,16 @@
         <v>46</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4270,7 +4276,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -4299,10 +4305,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4325,13 +4331,13 @@
         <v>46</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4382,7 +4388,7 @@
         <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -4391,7 +4397,7 @@
         <v>45</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>58</v>
@@ -4411,10 +4417,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4437,13 +4443,13 @@
         <v>35</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4494,7 +4500,7 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -4523,14 +4529,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4549,16 +4555,16 @@
         <v>35</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4596,19 +4602,19 @@
         <v>35</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -4620,7 +4626,7 @@
         <v>57</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>35</v>
@@ -4637,14 +4643,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4663,19 +4669,19 @@
         <v>46</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>35</v>
@@ -4724,7 +4730,7 @@
         <v>35</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -4736,7 +4742,7 @@
         <v>57</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>35</v>
@@ -4753,10 +4759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4782,13 +4788,13 @@
         <v>67</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4799,7 +4805,7 @@
         <v>35</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>35</v>
@@ -4814,13 +4820,13 @@
         <v>35</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>35</v>
@@ -4838,7 +4844,7 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>45</v>
@@ -4867,10 +4873,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4896,13 +4902,13 @@
         <v>60</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4952,7 +4958,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>45</v>
@@ -4981,10 +4987,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5007,16 +5013,16 @@
         <v>46</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5066,7 +5072,7 @@
         <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5095,10 +5101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5121,16 +5127,16 @@
         <v>46</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5180,7 +5186,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5209,10 +5215,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5235,16 +5241,16 @@
         <v>46</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5294,7 +5300,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -5323,10 +5329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5349,16 +5355,16 @@
         <v>46</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5408,7 +5414,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -5437,10 +5443,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5463,13 +5469,13 @@
         <v>46</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5520,7 +5526,7 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -5529,7 +5535,7 @@
         <v>45</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>58</v>
@@ -5549,10 +5555,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5575,13 +5581,13 @@
         <v>35</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5632,7 +5638,7 @@
         <v>35</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
@@ -5661,14 +5667,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5687,16 +5693,16 @@
         <v>35</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5734,19 +5740,19 @@
         <v>35</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -5758,7 +5764,7 @@
         <v>57</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>35</v>
@@ -5775,14 +5781,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5801,19 +5807,19 @@
         <v>46</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>35</v>
@@ -5862,7 +5868,7 @@
         <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -5874,7 +5880,7 @@
         <v>57</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>35</v>
@@ -5891,10 +5897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5917,16 +5923,16 @@
         <v>46</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5976,7 +5982,7 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>45</v>
@@ -6005,10 +6011,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6034,13 +6040,13 @@
         <v>60</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6090,7 +6096,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6119,10 +6125,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6145,16 +6151,16 @@
         <v>46</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6204,7 +6210,7 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -6233,10 +6239,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6259,16 +6265,16 @@
         <v>46</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6318,7 +6324,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -6347,10 +6353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6373,16 +6379,16 @@
         <v>46</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6432,7 +6438,7 @@
         <v>35</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -6450,7 +6456,7 @@
         <v>35</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>35</v>
@@ -6461,10 +6467,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6487,19 +6493,19 @@
         <v>46</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>35</v>
@@ -6548,7 +6554,7 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-22T12:19:21+00:00</t>
+    <t>2023-09-25T11:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-25T11:57:57+00:00</t>
+    <t>2023-10-02T07:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T07:48:38+00:00</t>
+    <t>2023-10-02T08:19:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T08:19:52+00:00</t>
+    <t>2023-10-02T10:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -476,6 +476,13 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
+    <t xml:space="preserve">profile:resource}
+</t>
+  </si>
+  <si>
+    <t>Slicing based on the profile conformance of the entry</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
@@ -516,6 +523,265 @@
     <t>Bundle.entry.resource</t>
   </si>
   <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>A resource in the bundle</t>
+  </si>
+  <si>
+    <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
+  </si>
+  <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search</t>
+  </si>
+  <si>
+    <t>Search related information</t>
+  </si>
+  <si>
+    <t>Information about the search process that lead to the creation of this entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-2</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.mode</t>
+  </si>
+  <si>
+    <t>match | include | outcome - why this is in the result set</t>
+  </si>
+  <si>
+    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
+  </si>
+  <si>
+    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Search ranking (between 0 and 1)</t>
+  </si>
+  <si>
+    <t>When searching, the server's search ranking score for the entry.</t>
+  </si>
+  <si>
+    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
+See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request</t>
+  </si>
+  <si>
+    <t>Additional execution information (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-3</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.method</t>
+  </si>
+  <si>
+    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+  </si>
+  <si>
+    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+  </si>
+  <si>
+    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.url</t>
+  </si>
+  <si>
+    <t>URL for HTTP equivalent of this entry</t>
+  </si>
+  <si>
+    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
+  </si>
+  <si>
+    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>For managing cache currency</t>
+  </si>
+  <si>
+    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifMatch</t>
+  </si>
+  <si>
+    <t>For managing update contention</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>For conditional creates</t>
+  </si>
+  <si>
+    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response</t>
+  </si>
+  <si>
+    <t>Results of execution (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
+  </si>
+  <si>
+    <t>ele-1
+bdl-4</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.status</t>
+  </si>
+  <si>
+    <t>Status response code (text optional)</t>
+  </si>
+  <si>
+    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.location</t>
+  </si>
+  <si>
+    <t>The location (if the operation returns a location)</t>
+  </si>
+  <si>
+    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.etag</t>
+  </si>
+  <si>
+    <t>The Etag for the resource (if relevant)</t>
+  </si>
+  <si>
+    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
+  </si>
+  <si>
+    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.lastModified</t>
+  </si>
+  <si>
+    <t>Server's date time modified</t>
+  </si>
+  <si>
+    <t>The date/time that the resource was modified on the server.</t>
+  </si>
+  <si>
+    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.outcome</t>
+  </si>
+  <si>
+    <t>OperationOutcome with hints and warnings (for batch/transaction)</t>
+  </si>
+  <si>
+    <t>An OperationOutcome containing hints and warnings produced as part of processing this entry in a batch or transaction.</t>
+  </si>
+  <si>
+    <t>For a POST/PUT operation, this is the equivalent outcome that would be returned for prefer = operationoutcome - except that the resource is always returned whether or not the outcome is returned.
+This outcome is not used for error responses in batch/transaction, only for hints and warnings. In a batch operation, the error will be in Bundle.entry.response, and for transaction, there will be a single OperationOutcome instead of a bundle in the case of an error.</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference</t>
+  </si>
+  <si>
+    <t>DUIDocumentReference</t>
+  </si>
+  <si>
+    <t>DocumentReference conforming to the TDDUIDocumentReference profile, used to convey a document in CDA format.</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.resource</t>
+  </si>
+  <si>
     <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-documentreference}
 </t>
   </si>
@@ -539,233 +805,82 @@
     <t>when describing a CDA</t>
   </si>
   <si>
-    <t>Bundle.entry.search</t>
-  </si>
-  <si>
-    <t>Search related information</t>
-  </si>
-  <si>
-    <t>Information about the search process that lead to the creation of this entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-2</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.mode</t>
-  </si>
-  <si>
-    <t>match | include | outcome - why this is in the result set</t>
-  </si>
-  <si>
-    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
-  </si>
-  <si>
-    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Search ranking (between 0 and 1)</t>
-  </si>
-  <si>
-    <t>When searching, the server's search ranking score for the entry.</t>
-  </si>
-  <si>
-    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
-See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request</t>
-  </si>
-  <si>
-    <t>Additional execution information (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-3</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.method</t>
-  </si>
-  <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
-  </si>
-  <si>
-    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+    <t>Bundle.entry:DUIDocumentReference.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.method</t>
   </si>
   <si>
     <t>POST</t>
   </si>
   <si>
-    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.url</t>
-  </si>
-  <si>
-    <t>URL for HTTP equivalent of this entry</t>
-  </si>
-  <si>
-    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
-  </si>
-  <si>
-    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>For managing cache currency</t>
-  </si>
-  <si>
-    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifMatch</t>
-  </si>
-  <si>
-    <t>For managing update contention</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>For conditional creates</t>
-  </si>
-  <si>
-    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response</t>
-  </si>
-  <si>
-    <t>Results of execution (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
-  </si>
-  <si>
-    <t>ele-1
-bdl-4</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.status</t>
-  </si>
-  <si>
-    <t>Status response code (text optional)</t>
-  </si>
-  <si>
-    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.location</t>
-  </si>
-  <si>
-    <t>The location (if the operation returns a location)</t>
-  </si>
-  <si>
-    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.etag</t>
-  </si>
-  <si>
-    <t>The Etag for the resource (if relevant)</t>
-  </si>
-  <si>
-    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
-  </si>
-  <si>
-    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.lastModified</t>
-  </si>
-  <si>
-    <t>Server's date time modified</t>
-  </si>
-  <si>
-    <t>The date/time that the resource was modified on the server.</t>
-  </si>
-  <si>
-    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>OperationOutcome with hints and warnings (for batch/transaction)</t>
-  </si>
-  <si>
-    <t>An OperationOutcome containing hints and warnings produced as part of processing this entry in a batch or transaction.</t>
-  </si>
-  <si>
-    <t>For a POST/PUT operation, this is the equivalent outcome that would be returned for prefer = operationoutcome - except that the resource is always returned whether or not the outcome is returned.
-This outcome is not used for error responses in batch/transaction, only for hints and warnings. In a batch operation, the error will be in Bundle.entry.response, and for transaction, there will be a single OperationOutcome instead of a bundle in the case of an error.</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
+    <t>Bundle.entry:DUIDocumentReference.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIDocumentReference.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1078,11 +1193,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.0078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.7734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.0078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
@@ -1105,14 +1221,13 @@
     <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="16.66796875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="50.03125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.98046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="17" max="17" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="62.87890625" customWidth="true" bestFit="true"/>
@@ -2900,16 +3015,16 @@
         <v>35</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>141</v>
@@ -2924,7 +3039,7 @@
         <v>57</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>35</v>
@@ -2941,10 +3056,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3053,10 +3168,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3167,10 +3282,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3283,10 +3398,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3312,10 +3427,10 @@
         <v>38</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3366,7 +3481,7 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
@@ -3395,10 +3510,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3424,13 +3539,13 @@
         <v>60</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3480,7 +3595,7 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -3509,10 +3624,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3520,7 +3635,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>45</v>
@@ -3532,20 +3647,18 @@
         <v>35</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>35</v>
@@ -3594,7 +3707,7 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -3606,7 +3719,7 @@
         <v>35</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>35</v>
@@ -3615,7 +3728,7 @@
         <v>161</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>35</v>
@@ -3623,10 +3736,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3652,10 +3765,10 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3706,7 +3819,7 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -3715,7 +3828,7 @@
         <v>45</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>58</v>
@@ -3735,10 +3848,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3847,10 +3960,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3961,10 +4074,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4077,10 +4190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4106,13 +4219,13 @@
         <v>67</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4141,11 +4254,11 @@
         <v>89</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>35</v>
       </c>
@@ -4162,7 +4275,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -4191,10 +4304,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4217,16 +4330,16 @@
         <v>46</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4276,7 +4389,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -4305,10 +4418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4334,10 +4447,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4388,7 +4501,7 @@
         <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -4397,7 +4510,7 @@
         <v>45</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>58</v>
@@ -4417,10 +4530,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4529,10 +4642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4643,10 +4756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4759,10 +4872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4788,10 +4901,10 @@
         <v>67</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>136</v>
@@ -4805,7 +4918,7 @@
         <v>35</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>191</v>
+        <v>35</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>35</v>
@@ -4823,10 +4936,10 @@
         <v>89</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>35</v>
@@ -4844,7 +4957,7 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>45</v>
@@ -4873,10 +4986,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4902,13 +5015,13 @@
         <v>60</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4958,7 +5071,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>45</v>
@@ -4987,10 +5100,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5016,10 +5129,10 @@
         <v>112</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>136</v>
@@ -5072,7 +5185,7 @@
         <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5101,10 +5214,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5130,13 +5243,13 @@
         <v>94</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5186,7 +5299,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5215,10 +5328,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5244,10 +5357,10 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>136</v>
@@ -5300,7 +5413,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -5329,10 +5442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5358,10 +5471,10 @@
         <v>112</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>136</v>
@@ -5414,7 +5527,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -5443,10 +5556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5472,10 +5585,10 @@
         <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5526,7 +5639,7 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -5535,7 +5648,7 @@
         <v>45</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>58</v>
@@ -5555,10 +5668,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5667,10 +5780,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5781,10 +5894,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5897,10 +6010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5926,10 +6039,10 @@
         <v>112</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>136</v>
@@ -5982,7 +6095,7 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>45</v>
@@ -6011,10 +6124,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6040,10 +6153,10 @@
         <v>60</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>140</v>
@@ -6096,7 +6209,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6125,10 +6238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6154,13 +6267,13 @@
         <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6210,7 +6323,7 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -6239,10 +6352,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6268,13 +6381,13 @@
         <v>94</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6324,7 +6437,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -6353,10 +6466,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6379,16 +6492,16 @@
         <v>46</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6438,7 +6551,7 @@
         <v>35</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -6456,7 +6569,7 @@
         <v>35</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>236</v>
+        <v>161</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>35</v>
@@ -6467,18 +6580,20 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>45</v>
@@ -6493,20 +6608,16 @@
         <v>46</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>238</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>35</v>
       </c>
@@ -6554,30 +6665,3672 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="AK48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AK53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>35</v>
       </c>
     </row>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T10:10:17+00:00</t>
+    <t>2023-10-02T11:49:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T11:49:05+00:00</t>
+    <t>2023-10-02T12:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-02T12:02:40+00:00</t>
+    <t>2023-10-03T08:22:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-03T08:22:32+00:00</t>
+    <t>2023-10-04T13:47:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-04T13:47:01+00:00</t>
+    <t>2023-10-05T12:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-05T12:28:13+00:00</t>
+    <t>2023-10-05T13:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-05T13:01:35+00:00</t>
+    <t>2023-10-06T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T10:30:12+00:00</t>
+    <t>2023-10-06T12:10:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T12:10:03+00:00</t>
+    <t>2023-10-06T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-06T14:30:45+00:00</t>
+    <t>2023-10-09T06:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T06:42:29+00:00</t>
+    <t>2023-10-09T14:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
